--- a/Sources/اجمالى A4-A5- تقرير المستهدف.xlsx
+++ b/Sources/اجمالى A4-A5- تقرير المستهدف.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E93800A-639C-4A50-A50E-40BCECF6ED02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD84EB4-E678-49CA-996A-9E7A01D7D112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="330" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -432,10 +432,10 @@
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -487,218 +487,6 @@
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
         <color rgb="FF000000"/>
         <name val="Arial"/>
         <family val="2"/>
@@ -1195,6 +983,218 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1209,29 +1209,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{888D4127-24A4-4C88-8554-06CB167E07BA}" name="Table1" displayName="Table1" ref="A1:G60" totalsRowCount="1" headerRowDxfId="29" dataDxfId="27" totalsRowDxfId="25" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{888D4127-24A4-4C88-8554-06CB167E07BA}" name="Table1" displayName="Table1" ref="A1:G60" totalsRowCount="1" headerRowDxfId="19" dataDxfId="17" totalsRowDxfId="15" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="14">
   <autoFilter ref="A1:G59" xr:uid="{888D4127-24A4-4C88-8554-06CB167E07BA}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A8C171E0-E180-4E76-8686-F51029A0AAC2}" name="القطاعات" totalsRowLabel="كفر الشيخ" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{72168A13-FDA6-4133-A6DD-45F08E51FC1A}" name="المستهدف" totalsRowFunction="custom" dataDxfId="21" totalsRowDxfId="20">
+    <tableColumn id="1" xr3:uid="{A8C171E0-E180-4E76-8686-F51029A0AAC2}" name="القطاعات" totalsRowLabel="كفر الشيخ" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{72168A13-FDA6-4133-A6DD-45F08E51FC1A}" name="المستهدف" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="10">
       <totalsRowFormula>SUBTOTAL(109,B43:B59)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7C6015EA-CE4E-469A-89A9-A8634BE2BE92}" name=" المنفذ" totalsRowFunction="custom" dataDxfId="19" totalsRowDxfId="18">
+    <tableColumn id="3" xr3:uid="{7C6015EA-CE4E-469A-89A9-A8634BE2BE92}" name=" المنفذ" totalsRowFunction="custom" dataDxfId="9" totalsRowDxfId="8">
       <totalsRowFormula>SUBTOTAL(109,C43:C59)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{F37D85AB-D72F-48D7-8314-BB296B97AAA8}" name="المتبقى" totalsRowFunction="custom" dataDxfId="17" totalsRowDxfId="16">
+    <tableColumn id="4" xr3:uid="{F37D85AB-D72F-48D7-8314-BB296B97AAA8}" name="المتبقى" totalsRowFunction="custom" dataDxfId="7" totalsRowDxfId="6">
       <calculatedColumnFormula>Table1[[#This Row],[المستهدف]]-Table1[[#This Row],[ المنفذ]]</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109,D43:D59)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8653D596-B69D-42F5-975E-1BB63681EC3E}" name="نسبة تنفيذ" totalsRowFunction="custom" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Percent" totalsRowCellStyle="Percent">
+    <tableColumn id="5" xr3:uid="{8653D596-B69D-42F5-975E-1BB63681EC3E}" name="نسبة تنفيذ" totalsRowFunction="custom" dataDxfId="5" totalsRowDxfId="4" dataCellStyle="Percent" totalsRowCellStyle="Percent">
       <calculatedColumnFormula>Table1[[#This Row],[ المنفذ]]/Table1[[#This Row],[المستهدف]]</calculatedColumnFormula>
       <totalsRowFormula>(C60/B60)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{BA9A909C-60C5-4116-96F9-7763535719C0}" name="المستهدف - الأسبوعي" totalsRowFunction="custom" dataDxfId="13" totalsRowDxfId="12">
+    <tableColumn id="6" xr3:uid="{BA9A909C-60C5-4116-96F9-7763535719C0}" name="المستهدف - الأسبوعي" totalsRowFunction="custom" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>Table1[[#This Row],[المتبقى]]/8</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109,F43:F59)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A3E55FE8-3CF0-4053-A2F1-0DCEEFD082AE}" name="المستهدف اليومي" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="10">
+    <tableColumn id="7" xr3:uid="{A3E55FE8-3CF0-4053-A2F1-0DCEEFD082AE}" name="المستهدف اليومي" totalsRowFunction="custom" dataDxfId="1" totalsRowDxfId="0">
       <calculatedColumnFormula>Table1[[#This Row],[المتبقى]]/6</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109,G43:G59)</totalsRowFormula>
     </tableColumn>
@@ -1241,11 +1241,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{221D51DB-CD87-4E30-BD2D-EF588B55E67B}" name="Table13" displayName="Table13" ref="A1:B60" totalsRowCount="1" headerRowDxfId="9" dataDxfId="8" totalsRowDxfId="7" headerRowBorderDxfId="5" tableBorderDxfId="6" totalsRowBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{221D51DB-CD87-4E30-BD2D-EF588B55E67B}" name="Table13" displayName="Table13" ref="A1:B60" totalsRowCount="1" headerRowDxfId="29" dataDxfId="27" totalsRowDxfId="25" headerRowBorderDxfId="28" tableBorderDxfId="26" totalsRowBorderDxfId="24">
   <autoFilter ref="A1:B59" xr:uid="{221D51DB-CD87-4E30-BD2D-EF588B55E67B}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7CDA3848-0114-419B-AA17-E16FD9827C2F}" name="القطاعات" totalsRowLabel="كفر الشيخ" dataDxfId="3" totalsRowDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{3D1166B7-4B94-4478-ADFD-C5CF664CCF7F}" name="A4-A5" totalsRowFunction="custom" dataDxfId="2" totalsRowDxfId="0">
+    <tableColumn id="1" xr3:uid="{7CDA3848-0114-419B-AA17-E16FD9827C2F}" name="القطاعات" totalsRowLabel="كفر الشيخ" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{3D1166B7-4B94-4478-ADFD-C5CF664CCF7F}" name="A4-A5" totalsRowFunction="custom" dataDxfId="21" totalsRowDxfId="20">
       <totalsRowFormula>SUBTOTAL(109,B43:B59)</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -3226,13 +3226,13 @@
         <v>193</v>
       </c>
       <c r="C2" s="8">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="D2" s="8">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="E2" s="8">
-        <v>193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3243,13 +3243,13 @@
         <v>324</v>
       </c>
       <c r="C3" s="8">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="D3" s="8">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="E3" s="8">
-        <v>324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3260,13 +3260,13 @@
         <v>271</v>
       </c>
       <c r="C4" s="8">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="D4" s="8">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="E4" s="8">
-        <v>271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3277,13 +3277,13 @@
         <v>240</v>
       </c>
       <c r="C5" s="8">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="D5" s="8">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="E5" s="8">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3294,13 +3294,13 @@
         <v>421</v>
       </c>
       <c r="C6" s="8">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="D6" s="8">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="E6" s="8">
-        <v>421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3311,13 +3311,13 @@
         <v>223</v>
       </c>
       <c r="C7" s="8">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="D7" s="8">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="E7" s="8">
-        <v>223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3328,13 +3328,13 @@
         <v>364</v>
       </c>
       <c r="C8" s="8">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="D8" s="8">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="E8" s="8">
-        <v>364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3345,13 +3345,13 @@
         <v>254</v>
       </c>
       <c r="C9" s="8">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="D9" s="8">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="E9" s="8">
-        <v>254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3362,13 +3362,13 @@
         <v>308</v>
       </c>
       <c r="C10" s="8">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="D10" s="8">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="E10" s="8">
-        <v>308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3379,13 +3379,13 @@
         <v>230</v>
       </c>
       <c r="C11" s="8">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="D11" s="8">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8">
-        <v>230</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3396,13 +3396,13 @@
         <v>260</v>
       </c>
       <c r="C12" s="8">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="D12" s="8">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="E12" s="8">
-        <v>260</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3413,13 +3413,13 @@
         <v>296</v>
       </c>
       <c r="C13" s="8">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="D13" s="8">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="E13" s="8">
-        <v>296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3430,13 +3430,13 @@
         <v>119</v>
       </c>
       <c r="C14" s="8">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="D14" s="8">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="E14" s="8">
-        <v>119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3447,13 +3447,13 @@
         <v>297</v>
       </c>
       <c r="C15" s="8">
-        <v>297</v>
+        <v>0</v>
       </c>
       <c r="D15" s="8">
-        <v>297</v>
+        <v>0</v>
       </c>
       <c r="E15" s="8">
-        <v>297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3466,15 +3466,15 @@
       </c>
       <c r="C16" s="15">
         <f>SUBTOTAL(109,C2:C15)</f>
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="D16" s="15">
         <f>SUBTOTAL(109,D2:D15)</f>
-        <v>3800</v>
+        <v>0</v>
       </c>
       <c r="E16" s="15">
         <f>SUBTOTAL(109,E2:E15)</f>
-        <v>3800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3485,13 +3485,13 @@
         <v>310</v>
       </c>
       <c r="C17" s="8">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="D17" s="8">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="E17" s="8">
-        <v>310</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3502,13 +3502,13 @@
         <v>535</v>
       </c>
       <c r="C18" s="8">
-        <v>535</v>
+        <v>0</v>
       </c>
       <c r="D18" s="8">
-        <v>535</v>
+        <v>0</v>
       </c>
       <c r="E18" s="8">
-        <v>535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3519,13 +3519,13 @@
         <v>250</v>
       </c>
       <c r="C19" s="8">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="D19" s="8">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E19" s="8">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3536,13 +3536,13 @@
         <v>95</v>
       </c>
       <c r="C20" s="8">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="D20" s="8">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="E20" s="8">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3553,13 +3553,13 @@
         <v>829</v>
       </c>
       <c r="C21" s="8">
-        <v>829</v>
+        <v>0</v>
       </c>
       <c r="D21" s="8">
-        <v>829</v>
+        <v>0</v>
       </c>
       <c r="E21" s="8">
-        <v>829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3570,13 +3570,13 @@
         <v>232</v>
       </c>
       <c r="C22" s="8">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="D22" s="8">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="E22" s="8">
-        <v>232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3587,13 +3587,13 @@
         <v>162</v>
       </c>
       <c r="C23" s="8">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="D23" s="8">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="E23" s="8">
-        <v>162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3604,13 +3604,13 @@
         <v>434</v>
       </c>
       <c r="C24" s="8">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="D24" s="8">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="E24" s="8">
-        <v>434</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3621,13 +3621,13 @@
         <v>369</v>
       </c>
       <c r="C25" s="8">
-        <v>369</v>
+        <v>0</v>
       </c>
       <c r="D25" s="8">
-        <v>369</v>
+        <v>0</v>
       </c>
       <c r="E25" s="8">
-        <v>369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3638,13 +3638,13 @@
         <v>281</v>
       </c>
       <c r="C26" s="8">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="D26" s="8">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="E26" s="8">
-        <v>281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3655,13 +3655,13 @@
         <v>299</v>
       </c>
       <c r="C27" s="8">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="D27" s="8">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="E27" s="8">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3674,15 +3674,15 @@
       </c>
       <c r="C28" s="15">
         <f>SUBTOTAL(109,C17:C27)</f>
-        <v>3796</v>
+        <v>0</v>
       </c>
       <c r="D28" s="15">
         <f>SUBTOTAL(109,D17:D27)</f>
-        <v>3796</v>
+        <v>0</v>
       </c>
       <c r="E28" s="15">
         <f>SUBTOTAL(109,E17:E27)</f>
-        <v>3796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3693,13 +3693,13 @@
         <v>707</v>
       </c>
       <c r="C29" s="8">
-        <v>707</v>
+        <v>0</v>
       </c>
       <c r="D29" s="8">
-        <v>707</v>
+        <v>0</v>
       </c>
       <c r="E29" s="8">
-        <v>707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3710,13 +3710,13 @@
         <v>880</v>
       </c>
       <c r="C30" s="8">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="D30" s="8">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="E30" s="8">
-        <v>880</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3727,13 +3727,13 @@
         <v>637</v>
       </c>
       <c r="C31" s="8">
-        <v>637</v>
+        <v>0</v>
       </c>
       <c r="D31" s="8">
-        <v>637</v>
+        <v>0</v>
       </c>
       <c r="E31" s="8">
-        <v>637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3744,13 +3744,13 @@
         <v>371</v>
       </c>
       <c r="C32" s="8">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="D32" s="8">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="E32" s="8">
-        <v>371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3761,13 +3761,13 @@
         <v>497</v>
       </c>
       <c r="C33" s="8">
-        <v>497</v>
+        <v>0</v>
       </c>
       <c r="D33" s="8">
-        <v>497</v>
+        <v>0</v>
       </c>
       <c r="E33" s="8">
-        <v>497</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3778,13 +3778,13 @@
         <v>387</v>
       </c>
       <c r="C34" s="8">
-        <v>387</v>
+        <v>0</v>
       </c>
       <c r="D34" s="8">
-        <v>387</v>
+        <v>0</v>
       </c>
       <c r="E34" s="8">
-        <v>387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3795,13 +3795,13 @@
         <v>760</v>
       </c>
       <c r="C35" s="8">
-        <v>760</v>
+        <v>0</v>
       </c>
       <c r="D35" s="8">
-        <v>760</v>
+        <v>0</v>
       </c>
       <c r="E35" s="8">
-        <v>760</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3812,13 +3812,13 @@
         <v>139</v>
       </c>
       <c r="C36" s="8">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="D36" s="8">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="E36" s="8">
-        <v>139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3829,13 +3829,13 @@
         <v>571</v>
       </c>
       <c r="C37" s="8">
-        <v>571</v>
+        <v>0</v>
       </c>
       <c r="D37" s="8">
-        <v>571</v>
+        <v>0</v>
       </c>
       <c r="E37" s="8">
-        <v>571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3846,13 +3846,13 @@
         <v>275</v>
       </c>
       <c r="C38" s="8">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="D38" s="8">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="E38" s="8">
-        <v>275</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3863,13 +3863,13 @@
         <v>339</v>
       </c>
       <c r="C39" s="8">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="D39" s="8">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="E39" s="8">
-        <v>339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3880,13 +3880,13 @@
         <v>475</v>
       </c>
       <c r="C40" s="8">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="D40" s="8">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="E40" s="8">
-        <v>475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3897,13 +3897,13 @@
         <v>345</v>
       </c>
       <c r="C41" s="8">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="D41" s="8">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E41" s="8">
-        <v>345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3916,15 +3916,15 @@
       </c>
       <c r="C42" s="15">
         <f>SUBTOTAL(109,C29:C41)</f>
-        <v>6383</v>
+        <v>0</v>
       </c>
       <c r="D42" s="15">
         <f>SUBTOTAL(109,D29:D41)</f>
-        <v>6383</v>
+        <v>0</v>
       </c>
       <c r="E42" s="15">
         <f>SUBTOTAL(109,E29:E41)</f>
-        <v>6383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3935,13 +3935,13 @@
         <v>446</v>
       </c>
       <c r="C43" s="8">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="D43" s="8">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="E43" s="8">
-        <v>446</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3952,13 +3952,13 @@
         <v>357</v>
       </c>
       <c r="C44" s="8">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="D44" s="8">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="E44" s="8">
-        <v>357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3969,13 +3969,13 @@
         <v>332</v>
       </c>
       <c r="C45" s="8">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="D45" s="8">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="E45" s="8">
-        <v>332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3986,13 +3986,13 @@
         <v>313</v>
       </c>
       <c r="C46" s="8">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="D46" s="8">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="E46" s="8">
-        <v>313</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4003,13 +4003,13 @@
         <v>389</v>
       </c>
       <c r="C47" s="8">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="D47" s="8">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="E47" s="8">
-        <v>389</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4020,13 +4020,13 @@
         <v>353</v>
       </c>
       <c r="C48" s="8">
-        <v>353</v>
+        <v>0</v>
       </c>
       <c r="D48" s="8">
-        <v>353</v>
+        <v>0</v>
       </c>
       <c r="E48" s="8">
-        <v>353</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4037,13 +4037,13 @@
         <v>435</v>
       </c>
       <c r="C49" s="8">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="D49" s="8">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="E49" s="8">
-        <v>435</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4054,13 +4054,13 @@
         <v>201</v>
       </c>
       <c r="C50" s="8">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="D50" s="8">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="E50" s="8">
-        <v>201</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4071,13 +4071,13 @@
         <v>385</v>
       </c>
       <c r="C51" s="8">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="D51" s="8">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="E51" s="8">
-        <v>385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4088,13 +4088,13 @@
         <v>225</v>
       </c>
       <c r="C52" s="8">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="D52" s="8">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="E52" s="8">
-        <v>225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4105,13 +4105,13 @@
         <v>332</v>
       </c>
       <c r="C53" s="8">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="D53" s="8">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="E53" s="8">
-        <v>332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4122,13 +4122,13 @@
         <v>586</v>
       </c>
       <c r="C54" s="8">
-        <v>586</v>
+        <v>0</v>
       </c>
       <c r="D54" s="8">
-        <v>586</v>
+        <v>0</v>
       </c>
       <c r="E54" s="8">
-        <v>586</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4139,13 +4139,13 @@
         <v>243</v>
       </c>
       <c r="C55" s="8">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="D55" s="8">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="E55" s="8">
-        <v>243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4156,13 +4156,13 @@
         <v>333</v>
       </c>
       <c r="C56" s="8">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="D56" s="8">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="E56" s="8">
-        <v>333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4173,13 +4173,13 @@
         <v>502</v>
       </c>
       <c r="C57" s="8">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="D57" s="8">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="E57" s="8">
-        <v>502</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4190,13 +4190,13 @@
         <v>365</v>
       </c>
       <c r="C58" s="8">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="D58" s="8">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="E58" s="8">
-        <v>365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4207,13 +4207,13 @@
         <v>155</v>
       </c>
       <c r="C59" s="8">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="D59" s="8">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="E59" s="8">
-        <v>155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4226,15 +4226,15 @@
       </c>
       <c r="C60" s="15">
         <f>SUBTOTAL(109,C43:C59)</f>
-        <v>5952</v>
+        <v>0</v>
       </c>
       <c r="D60" s="15">
         <f>SUBTOTAL(109,D43:D59)</f>
-        <v>5952</v>
+        <v>0</v>
       </c>
       <c r="E60" s="15">
         <f>SUBTOTAL(109,E43:E59)</f>
-        <v>5952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4247,15 +4247,15 @@
       </c>
       <c r="C61" s="10">
         <f>C16+C28+C42+Table13[[#Totals],[A4-A5]]</f>
-        <v>19931</v>
+        <v>5952</v>
       </c>
       <c r="D61" s="10">
         <f>D16+D28+D42+Table13[[#Totals],[A4-A5]]</f>
-        <v>19931</v>
+        <v>5952</v>
       </c>
       <c r="E61" s="10">
         <f>E16+E28+E42+Table13[[#Totals],[A4-A5]]</f>
-        <v>19931</v>
+        <v>5952</v>
       </c>
     </row>
   </sheetData>
@@ -4281,15 +4281,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -4706,7 +4706,7 @@
         <f t="shared" si="4"/>
         <v>1139</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="19">
         <f t="shared" si="1"/>
         <v>0.70026315789473681</v>
       </c>
@@ -4741,15 +4741,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -5177,15 +5177,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -5523,7 +5523,7 @@
         <f t="shared" si="4"/>
         <v>3618</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="19">
         <f t="shared" si="1"/>
         <v>4.6891464699683881E-2</v>
       </c>
@@ -5559,15 +5559,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -6067,7 +6067,7 @@
         <f>SUBTOTAL(109,D3:D19)</f>
         <v>3097</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="19">
         <f t="shared" si="1"/>
         <v>0.47967069892473119</v>
       </c>
